--- a/output/伊勢赤十字病院_随意契約_X線関連.xlsx
+++ b/output/伊勢赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>乳房Ｘ線撮影装置保守契約</t>
+          <t>内視鏡用デジタルX線透視撮影装置 １式</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -585,30 +585,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月1日</t>
+          <t>令和5年10月10日</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>㈱エヌケーティー伊勢市御薗町長屋2026番地2</t>
+          <t>㈱八神製作所 伊勢営業所伊勢市神久二丁目１番２８号</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3080000</v>
+        <v>31526000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://www.ise.jrc.or.jp/file/attachment/6263.pdf</t>
+          <t>https://www.ise.jrc.or.jp/file/attachment/3638.pdf</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
@@ -616,7 +616,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ＦＰＤシステム保守契約</t>
+          <t>乳房Ｘ線撮影装置保守契約</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
@@ -627,33 +627,75 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>令和7年4月1日</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>㈱エヌケーティー伊勢市御薗町長屋2026番地2</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3080000</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ise.jrc.or.jp/file/attachment/6263.pdf</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ＦＰＤシステム保守契約</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>伊勢赤十字病院 事務部 資材課伊勢市船江１丁目４７１番２</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>令和6年3月29日</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>㈱エヌケーティー三重県伊勢市御薗町長屋2062-2</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>8360000</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>https://www.ise.jrc.or.jp/file/attachment/3638.pdf</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -716,13 +758,9 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -746,9 +784,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>公表された随意契約に該当なし</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
